--- a/03_Outputs/Turistica_Agroecologica/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/08_Educacion/educacion.xlsx
@@ -3982,13 +3982,13 @@
         <v>2021</v>
       </c>
       <c r="F109" s="7">
-        <v>0.854501579338908</v>
+        <v>0.805241335482816</v>
       </c>
       <c r="G109" s="9">
-        <v>0.0562292052820038</v>
+        <v>0.0650883320483166</v>
       </c>
       <c r="H109" s="11">
-        <v>0.0400637433203647</v>
+        <v>0.0828765215765987</v>
       </c>
     </row>
     <row r="110">
@@ -4016,13 +4016,13 @@
         <v>2021</v>
       </c>
       <c r="F110" s="7">
-        <v>0.751725461200452</v>
+        <v>0.839551588466629</v>
       </c>
       <c r="G110" s="9">
-        <v>0.0449901180989826</v>
+        <v>0.0579854236957749</v>
       </c>
       <c r="H110" s="11">
-        <v>0.0279247119161082</v>
+        <v>0.0699376159957595</v>
       </c>
     </row>
     <row r="111">
@@ -4050,13 +4050,13 @@
         <v>2021</v>
       </c>
       <c r="F111" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G111" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H111" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="112">
